--- a/agent_runs/manjidiwang/episodes/ep24/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep24/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>田立民强开表决（，总时长：10秒，镜头数：4个）</t>
+          <t>田立民强开表决</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>控股威胁与落座宣告（，总时长：11秒，镜头数：4个）</t>
+          <t>控股威胁与落座宣告</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>朱文浩带证入场（，总时长：10秒，镜头数：4个）</t>
+          <t>朱文浩带证入场</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>掀桌拔枪逼退全场（，总时长：11秒，镜头数：4个）</t>
+          <t>掀桌拔枪逼退全场</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>挟持李长庚索要直升机（，总时长：14秒，镜头数：5个）</t>
+          <t>挟持李长庚索要直升机</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>空枪试探被枪声击碎（，总时长：11秒，镜头数：5个）</t>
+          <t>空枪试探被枪声击碎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>遥控炸弹倒计时亮出（，总时长：11秒，镜头数：3个）</t>
+          <t>遥控炸弹倒计时亮出</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>朱文浩逼田立民不敢炸（，总时长：10秒，镜头数：4个）</t>
+          <t>朱文浩逼田立民不敢炸</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>炸弹信号被屏蔽（，总时长：10秒，镜头数：3个）</t>
+          <t>炸弹信号被屏蔽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>安防黑名单反制炸弹（，总时长：12秒，镜头数：4个）</t>
+          <t>安防黑名单反制炸弹</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>二十步落子带走田立民（，总时长：12秒，镜头数：5个）</t>
+          <t>二十步落子带走田立民</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>朱文浩耳语收局（，总时长：10秒，镜头数：3个）</t>
+          <t>朱文浩耳语收局</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
